--- a/output/pdf_financials_xlsx/OLA.xlsx
+++ b/output/pdf_financials_xlsx/OLA.xlsx
@@ -1302,25 +1302,25 @@
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.869269</v>
+        <v>-0.869269</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.142449</v>
+        <v>-0.142449</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.283496</v>
+        <v>-0.283496</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>2.890183</v>
+        <v>-2.890183</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>18.7</v>
+        <v>-18.7</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>29.913</v>
+        <v>-29.913</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>29.397</v>
+        <v>-29.397</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>-26.278</v>
@@ -1606,25 +1606,25 @@
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.869269</v>
+        <v>-0.869269</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.142449</v>
+        <v>-0.142449</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.283496</v>
+        <v>-0.283496</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>2.890183</v>
+        <v>-2.890183</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>18.7</v>
+        <v>-18.7</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>29.913</v>
+        <v>-29.913</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>29.397</v>
+        <v>-29.397</v>
       </c>
       <c r="N20" s="3" t="n">
         <v>2.733</v>
@@ -1786,25 +1786,25 @@
         </is>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.869269</v>
+        <v>-0.869269</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.142449</v>
+        <v>-0.142449</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.283496</v>
+        <v>-0.283496</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>2.890183</v>
+        <v>-2.890183</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>18.7</v>
+        <v>-18.7</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>29.913</v>
+        <v>-29.913</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>29.397</v>
+        <v>-29.397</v>
       </c>
       <c r="N23" s="3" t="n">
         <v>-26.278</v>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>4.346345</v>
+        <v>-4.346345</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>4.7483</v>
+        <v>-4.7483</v>
       </c>
       <c r="I26" s="1" t="inlineStr">
         <is>
@@ -1992,13 +1992,13 @@
         </is>
       </c>
       <c r="K26" s="3" t="n">
-        <v>124.666667</v>
+        <v>-124.666667</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>175.958824</v>
+        <v>-175.958824</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>183.73125</v>
+        <v>-183.73125</v>
       </c>
       <c r="N26" s="3" t="n">
         <v>238.890909</v>
@@ -2040,25 +2040,25 @@
         </is>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.869269</v>
+        <v>-0.869269</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.142449</v>
+        <v>-0.142449</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.283496</v>
+        <v>-0.283496</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>2.890183</v>
+        <v>-2.890183</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>18.7</v>
+        <v>-18.7</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>29.913</v>
+        <v>-29.913</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>29.397</v>
+        <v>-29.397</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>-26.278</v>
@@ -2160,25 +2160,25 @@
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.869269</v>
+        <v>-0.869269</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.142449</v>
+        <v>-0.142449</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.283496</v>
+        <v>-0.283496</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>2.891432</v>
+        <v>-2.888934</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>18.889</v>
+        <v>-18.511</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>30.066</v>
+        <v>-29.76</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>29.5</v>
+        <v>-29.294</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>-26.278</v>
@@ -2302,25 +2302,25 @@
         </is>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N31" s="3" t="n">
         <v>-0</v>
@@ -6046,46 +6046,46 @@
         <v>0.137815</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.178245</v>
+        <v>0.137815</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.273706</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.213501</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.239744</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.332544</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.782956</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>11.985482</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>11.985</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>25.96</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>39.348</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>29.306</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>24.009</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>24.387</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>25.182</v>
       </c>
       <c r="R92" s="1" t="inlineStr">
         <is>
@@ -7565,10 +7565,10 @@
         <v>0</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-0.214481</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-0.603815</v>
       </c>
       <c r="F118" s="1" t="inlineStr">
         <is>
@@ -7576,10 +7576,10 @@
         </is>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0.62285</v>
+        <v>0.594481</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0.070618</v>
+        <v>0.038026</v>
       </c>
       <c r="I118" s="3" t="n">
         <v>-0.002281</v>
@@ -11992,7 +11992,11 @@
           <t>Reserves 22,590</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>-</t>
@@ -14794,7 +14798,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
@@ -21074,7 +21082,11 @@
           <t>Reserves 25,960</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E123" t="inlineStr">
         <is>
           <t>-</t>
@@ -22680,7 +22692,11 @@
           <t>Reserves (note 9)</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E139" t="inlineStr">
         <is>
           <t>-</t>
@@ -24573,7 +24589,11 @@
           <t>Reserves (note 7)</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr"/>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr">
         <is>
           <t>-</t>
@@ -25658,7 +25678,11 @@
           <t>Share-based payment reserve 9</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr"/>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E169" t="inlineStr">
         <is>
           <t>-</t>
@@ -26571,7 +26595,11 @@
           <t>Share-based payment reserve 9</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr"/>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E178" t="inlineStr">
         <is>
           <t>-</t>
@@ -28211,7 +28239,11 @@
           <t>Share-based payments reserve (Note 9 and 10) 273,706</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr"/>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E194" t="inlineStr">
         <is>
           <t>-</t>
@@ -47598,7 +47630,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D387" t="inlineStr"/>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E387" t="inlineStr">
         <is>
           <t>-</t>
@@ -49731,7 +49767,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D408" t="inlineStr"/>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E408" t="inlineStr">
         <is>
           <t>-</t>
@@ -60548,19 +60588,19 @@
         </is>
       </c>
       <c r="L516" s="5" t="n">
-        <v>0.283496</v>
+        <v>-0.283496</v>
       </c>
       <c r="M516" s="5" t="n">
-        <v>2.890183</v>
+        <v>-2.890183</v>
       </c>
       <c r="N516" s="5" t="n">
-        <v>18.7</v>
+        <v>-18.7</v>
       </c>
       <c r="O516" s="5" t="n">
-        <v>29.913</v>
+        <v>-29.913</v>
       </c>
       <c r="P516" s="5" t="n">
-        <v>29.397</v>
+        <v>-29.397</v>
       </c>
       <c r="Q516" t="inlineStr">
         <is>
@@ -63252,10 +63292,10 @@
         </is>
       </c>
       <c r="M543" s="5" t="n">
-        <v>2.890183</v>
+        <v>-2.890183</v>
       </c>
       <c r="N543" s="5" t="n">
-        <v>9.925266000000001</v>
+        <v>-9.925266000000001</v>
       </c>
       <c r="O543" t="inlineStr">
         <is>
@@ -63454,10 +63494,10 @@
         </is>
       </c>
       <c r="M545" s="5" t="n">
-        <v>1.604584</v>
+        <v>-1.604584</v>
       </c>
       <c r="N545" s="5" t="n">
-        <v>20.050454</v>
+        <v>-20.050454</v>
       </c>
       <c r="O545" t="inlineStr">
         <is>
@@ -65249,10 +65289,10 @@
         </is>
       </c>
       <c r="L563" s="5" t="n">
-        <v>0.270496</v>
+        <v>-0.270496</v>
       </c>
       <c r="M563" s="5" t="n">
-        <v>1.604584</v>
+        <v>-1.604584</v>
       </c>
       <c r="N563" t="inlineStr">
         <is>
@@ -66867,10 +66907,10 @@
         </is>
       </c>
       <c r="J579" s="5" t="n">
-        <v>0.869269</v>
+        <v>-0.869269</v>
       </c>
       <c r="K579" s="5" t="n">
-        <v>0.142449</v>
+        <v>-0.142449</v>
       </c>
       <c r="L579" t="inlineStr">
         <is>
@@ -67069,10 +67109,10 @@
         </is>
       </c>
       <c r="J581" s="5" t="n">
-        <v>0.876269</v>
+        <v>-0.876269</v>
       </c>
       <c r="K581" s="5" t="n">
-        <v>0.143449</v>
+        <v>-0.143449</v>
       </c>
       <c r="L581" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/OLA.xlsx
+++ b/output/pdf_financials_xlsx/OLA.xlsx
@@ -942,10 +942,10 @@
         </is>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.129819</v>
+        <v>0.183744</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.033337</v>
+        <v>0.09891999999999999</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>0.25068</v>
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-0.129819</v>
+        <v>-0.183744</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-0.033337</v>
+        <v>-0.09891999999999999</v>
       </c>
       <c r="I11" s="3" t="n">
         <v>-0.25068</v>
@@ -1045,16 +1045,16 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.020996</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.003202</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.00112</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>1.7e-05</v>
       </c>
       <c r="F12" s="1" t="inlineStr">
         <is>
@@ -1068,34 +1068,34 @@
         <v>0</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.00053</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-0.066535</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-0.187</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-0.442</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>-0.142</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.341</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>2.167</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>5.387</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>10.845</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>8.321999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -2023,16 +2023,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.093862</v>
+        <v>-0.114858</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.210228</v>
+        <v>-0.21343</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.285551</v>
+        <v>-0.286671</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.235672</v>
+        <v>-0.235689</v>
       </c>
       <c r="F27" s="1" t="inlineStr">
         <is>
@@ -2046,34 +2046,34 @@
         <v>-0.142449</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.283496</v>
+        <v>-0.282966</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-2.890183</v>
+        <v>-2.823648</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-18.7</v>
+        <v>-18.513</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-29.913</v>
+        <v>-29.471</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-29.397</v>
+        <v>-29.255</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-26.278</v>
+        <v>-26.619</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>78.398</v>
+        <v>76.23099999999999</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>7.594</v>
+        <v>2.207</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>176.262</v>
+        <v>165.417</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>261.047</v>
+        <v>252.725</v>
       </c>
     </row>
     <row r="28">
@@ -2143,16 +2143,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.093862</v>
+        <v>-0.114858</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.210228</v>
+        <v>-0.21343</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.285551</v>
+        <v>-0.286671</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.235672</v>
+        <v>-0.235689</v>
       </c>
       <c r="F29" s="1" t="inlineStr">
         <is>
@@ -2166,34 +2166,34 @@
         <v>-0.142449</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.283496</v>
+        <v>-0.282966</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-2.888934</v>
+        <v>-2.822399</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-18.511</v>
+        <v>-18.324</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-29.76</v>
+        <v>-29.318</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-29.294</v>
+        <v>-29.152</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-26.278</v>
+        <v>-26.619</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>78.398</v>
+        <v>76.23099999999999</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>7.594</v>
+        <v>2.207</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>176.262</v>
+        <v>165.417</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>261.047</v>
+        <v>252.725</v>
       </c>
     </row>
     <row r="30">
@@ -2263,19 +2263,19 @@
         </is>
       </c>
       <c r="N30" s="3" t="n">
-        <v>-637.1968962172648</v>
+        <v>-645.4655674102812</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>40.57237489002743</v>
+        <v>39.45091341924132</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>3.250257872052662</v>
+        <v>0.9446035190440115</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>51.25117033711524</v>
+        <v>48.09780238312621</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>24.6764050020749</v>
+        <v>23.88973807072818</v>
       </c>
     </row>
     <row r="31">
@@ -2434,34 +2434,34 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.045675</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.09338200000000001</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.09338200000000001</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.09976</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.141771</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.039687</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.002427</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.418703</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>25.935149</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>25.935</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>16.686</v>
@@ -2479,7 +2479,7 @@
         <v>96.63200000000001</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>160.849</v>
       </c>
       <c r="R34" s="1" t="inlineStr">
         <is>
@@ -2554,34 +2554,34 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.045675</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.09338200000000001</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.09338200000000001</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.09976</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.141771</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.039687</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.002427</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.418703</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>25.935149</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>25.935</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>16.686</v>
@@ -2599,7 +2599,7 @@
         <v>96.63200000000001</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>160.849</v>
       </c>
       <c r="R36" s="1" t="inlineStr">
         <is>
@@ -3274,34 +3274,34 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.795675</v>
+        <v>0.75</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.593382</v>
+        <v>0.5</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.593382</v>
+        <v>0.5</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.143921</v>
+        <v>0.044161</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.165731</v>
+        <v>0.02396</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.047799</v>
+        <v>0.008111999999999999</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.002704</v>
+        <v>0.000277</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.431168</v>
+        <v>0.012465</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>26.703434</v>
+        <v>0.768285</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>26.294</v>
+        <v>0.359</v>
       </c>
       <c r="L48" s="3" t="n">
         <v>0.206</v>
@@ -3319,7 +3319,7 @@
         <v>18.713</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>175.178</v>
+        <v>14.329</v>
       </c>
       <c r="R48" s="1" t="inlineStr">
         <is>
@@ -7954,22 +7954,22 @@
         <v>0</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-0.034</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-0.649</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-0.574</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-0.969</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>0</v>
+        <v>-1.351</v>
       </c>
       <c r="R124" s="3" t="n">
-        <v>0</v>
+        <v>-2.488</v>
       </c>
     </row>
     <row r="125">
@@ -8014,22 +8014,22 @@
         <v>0</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-0.034</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-0.649</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-0.574</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-0.969</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>0</v>
+        <v>-1.351</v>
       </c>
       <c r="R125" s="3" t="n">
-        <v>0</v>
+        <v>-2.488</v>
       </c>
     </row>
     <row r="126">
@@ -9112,7 +9112,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -12519,7 +12519,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -19751,7 +19751,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -20058,7 +20058,11 @@
           <t>Reclamation deposits 205</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
           <t>-</t>
@@ -21985,7 +21989,11 @@
           <t>Reclamation deposits (note 5)</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
           <t>-</t>
@@ -23373,7 +23381,11 @@
           <t>Reclamation deposits (note 5)</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E146" t="inlineStr">
         <is>
           <t>-</t>
@@ -24890,7 +24902,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E161" s="5" t="n">
@@ -27108,7 +27120,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -33029,7 +33041,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D242" t="inlineStr"/>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E242" t="inlineStr">
         <is>
           <t>-</t>
@@ -39643,7 +39659,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D308" t="inlineStr"/>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E308" t="inlineStr">
         <is>
           <t>-</t>
@@ -52585,7 +52605,7 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
@@ -59949,7 +59969,7 @@
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E510" t="inlineStr">
@@ -60046,7 +60066,7 @@
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E511" t="inlineStr">
@@ -66375,7 +66395,7 @@
       </c>
       <c r="D574" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E574" t="inlineStr">
@@ -68484,7 +68504,7 @@
       </c>
       <c r="D595" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E595" t="inlineStr">
@@ -69702,7 +69722,7 @@
       </c>
       <c r="D607" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E607" s="5" t="n">

--- a/output/pdf_financials_xlsx/OLA.xlsx
+++ b/output/pdf_financials_xlsx/OLA.xlsx
@@ -7249,7 +7249,7 @@
         <v>0</v>
       </c>
       <c r="R112" s="3" t="n">
-        <v>0</v>
+        <v>0.492</v>
       </c>
     </row>
     <row r="113">
@@ -7708,19 +7708,19 @@
         <v>0</v>
       </c>
       <c r="K120" s="3" t="n">
-        <v>0</v>
+        <v>1.047</v>
       </c>
       <c r="L120" s="3" t="n">
-        <v>0</v>
+        <v>31.01</v>
       </c>
       <c r="M120" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N120" s="3" t="n">
-        <v>0</v>
+        <v>33.442</v>
       </c>
       <c r="O120" s="3" t="n">
-        <v>0</v>
+        <v>-0.261</v>
       </c>
       <c r="P120" s="3" t="n">
         <v>0</v>
@@ -32059,7 +32059,11 @@
           <t>Proceeds on disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D232" t="inlineStr"/>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E232" t="inlineStr">
         <is>
           <t>-</t>
@@ -37950,7 +37954,11 @@
           <t>Proceeds from issuance of common shares, net of issuance costs</t>
         </is>
       </c>
-      <c r="D291" t="inlineStr"/>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E291" t="inlineStr">
         <is>
           <t>-</t>
@@ -42782,7 +42790,11 @@
           <t>Proceeds on issuance of common shares, net of issuance costs</t>
         </is>
       </c>
-      <c r="D339" t="inlineStr"/>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E339" t="inlineStr">
         <is>
           <t>-</t>
